--- a/excel-files/PARANAQUE/MASVILLE ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/PARANAQUE/MASVILLE ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29721"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="159" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C0D6656-87D2-461F-8122-4156C305C80A}"/>
+  <xr:revisionPtr revIDLastSave="172" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{711DC8F8-A385-4660-9813-042856399238}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="94">
   <si>
     <t>Grade Level</t>
   </si>
@@ -676,34 +676,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thick">
         <color rgb="FF000000"/>
@@ -746,6 +718,30 @@
       </top>
       <bottom style="thin">
         <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -876,12 +872,6 @@
     <xf numFmtId="0" fontId="16" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -900,13 +890,13 @@
     <xf numFmtId="0" fontId="15" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -915,7 +905,7 @@
     <xf numFmtId="0" fontId="15" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -924,10 +914,16 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3657,7 +3653,7 @@
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.85546875" customWidth="1"/>
     <col min="3" max="3" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="119.5703125" customWidth="1"/>
+    <col min="4" max="4" width="45.28515625" customWidth="1"/>
     <col min="5" max="5" width="24.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="42.28515625" customWidth="1"/>
     <col min="7" max="7" width="30.85546875" customWidth="1"/>
@@ -3715,13 +3711,13 @@
       <c r="F2" s="42">
         <v>2024</v>
       </c>
-      <c r="G2" s="50" t="s">
+      <c r="G2" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="51">
-        <v>0</v>
-      </c>
-      <c r="I2" s="52">
+      <c r="H2" s="49">
+        <v>0</v>
+      </c>
+      <c r="I2" s="50">
         <v>4</v>
       </c>
     </row>
@@ -3732,21 +3728,21 @@
       <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="46">
+      <c r="C3" s="44">
         <v>266</v>
       </c>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48" t="s">
+      <c r="D3" s="46"/>
+      <c r="E3" s="46" t="s">
         <v>12</v>
       </c>
       <c r="F3" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="48"/>
-      <c r="H3" s="53">
+      <c r="G3" s="46"/>
+      <c r="H3" s="51">
         <v>266</v>
       </c>
-      <c r="I3" s="54">
+      <c r="I3" s="52">
         <v>0</v>
       </c>
     </row>
@@ -3757,23 +3753,23 @@
       <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="46">
+      <c r="C4" s="44">
         <v>266</v>
       </c>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48">
+      <c r="D4" s="46"/>
+      <c r="E4" s="46">
         <v>270</v>
       </c>
-      <c r="F4" s="48">
+      <c r="F4" s="46">
         <v>2024</v>
       </c>
-      <c r="G4" s="48" t="s">
+      <c r="G4" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="53">
-        <v>0</v>
-      </c>
-      <c r="I4" s="54">
+      <c r="H4" s="51">
+        <v>0</v>
+      </c>
+      <c r="I4" s="52">
         <v>4</v>
       </c>
     </row>
@@ -3784,23 +3780,23 @@
       <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="46">
+      <c r="C5" s="44">
         <v>266</v>
       </c>
-      <c r="D5" s="46"/>
+      <c r="D5" s="44"/>
       <c r="E5" s="42">
         <v>270</v>
       </c>
-      <c r="F5" s="48">
+      <c r="F5" s="46">
         <v>2024</v>
       </c>
-      <c r="G5" s="48" t="s">
+      <c r="G5" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="53">
-        <v>0</v>
-      </c>
-      <c r="I5" s="54">
+      <c r="H5" s="51">
+        <v>0</v>
+      </c>
+      <c r="I5" s="52">
         <v>4</v>
       </c>
     </row>
@@ -3811,23 +3807,23 @@
       <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="46">
+      <c r="C6" s="44">
         <v>266</v>
       </c>
-      <c r="D6" s="46"/>
+      <c r="D6" s="44"/>
       <c r="E6" s="42">
         <v>0</v>
       </c>
       <c r="F6" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="48" t="s">
+      <c r="G6" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="53">
+      <c r="H6" s="51">
         <v>266</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="52">
         <v>0</v>
       </c>
     </row>
@@ -3836,9 +3832,9 @@
       <c r="D7" s="43"/>
       <c r="E7" s="43"/>
       <c r="F7" s="43"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
     </row>
     <row r="8" spans="1:12" ht="39.75" customHeight="1">
       <c r="A8" s="1">
@@ -3857,13 +3853,13 @@
       <c r="F8" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="50" t="s">
+      <c r="G8" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="51">
+      <c r="H8" s="49">
         <v>282</v>
       </c>
-      <c r="I8" s="52">
+      <c r="I8" s="50">
         <v>0</v>
       </c>
     </row>
@@ -3874,23 +3870,23 @@
       <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="46">
+      <c r="C9" s="44">
         <v>282</v>
       </c>
-      <c r="D9" s="46"/>
+      <c r="D9" s="44"/>
       <c r="E9" s="42">
         <v>0</v>
       </c>
       <c r="F9" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="48" t="s">
+      <c r="G9" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="53">
+      <c r="H9" s="51">
         <v>282</v>
       </c>
-      <c r="I9" s="54">
+      <c r="I9" s="52">
         <v>0</v>
       </c>
     </row>
@@ -3901,23 +3897,23 @@
       <c r="B10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="46">
+      <c r="C10" s="44">
         <v>282</v>
       </c>
-      <c r="D10" s="46"/>
+      <c r="D10" s="44"/>
       <c r="E10" s="42">
         <v>0</v>
       </c>
       <c r="F10" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="48" t="s">
+      <c r="G10" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="53">
+      <c r="H10" s="51">
         <v>282</v>
       </c>
-      <c r="I10" s="54">
+      <c r="I10" s="52">
         <v>0</v>
       </c>
     </row>
@@ -3928,23 +3924,23 @@
       <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="46">
+      <c r="C11" s="44">
         <v>282</v>
       </c>
-      <c r="D11" s="46"/>
+      <c r="D11" s="44"/>
       <c r="E11" s="42">
         <v>0</v>
       </c>
       <c r="F11" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="48" t="s">
+      <c r="G11" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="53">
+      <c r="H11" s="51">
         <v>282</v>
       </c>
-      <c r="I11" s="54">
+      <c r="I11" s="52">
         <v>0</v>
       </c>
     </row>
@@ -3955,23 +3951,23 @@
       <c r="B12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="46">
+      <c r="C12" s="44">
         <v>282</v>
       </c>
-      <c r="D12" s="46"/>
+      <c r="D12" s="44"/>
       <c r="E12" s="42">
         <v>0</v>
       </c>
       <c r="F12" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="48" t="s">
+      <c r="G12" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="53">
+      <c r="H12" s="51">
         <v>282</v>
       </c>
-      <c r="I12" s="54">
+      <c r="I12" s="52">
         <v>0</v>
       </c>
     </row>
@@ -3980,9 +3976,9 @@
       <c r="D13" s="43"/>
       <c r="E13" s="43"/>
       <c r="F13" s="43"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="55"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="53"/>
     </row>
     <row r="14" spans="1:12" ht="49.5" customHeight="1">
       <c r="A14" s="1">
@@ -4001,13 +3997,13 @@
       <c r="F14" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G14" s="50" t="s">
+      <c r="G14" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="H14" s="51">
+      <c r="H14" s="49">
         <v>312</v>
       </c>
-      <c r="I14" s="52">
+      <c r="I14" s="50">
         <v>0</v>
       </c>
     </row>
@@ -4018,23 +4014,23 @@
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="46">
+      <c r="C15" s="44">
         <v>312</v>
       </c>
-      <c r="D15" s="46"/>
+      <c r="D15" s="44"/>
       <c r="E15" s="42">
         <v>0</v>
       </c>
       <c r="F15" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="48" t="s">
+      <c r="G15" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H15" s="53">
+      <c r="H15" s="51">
         <v>312</v>
       </c>
-      <c r="I15" s="54">
+      <c r="I15" s="52">
         <v>0</v>
       </c>
     </row>
@@ -4045,23 +4041,23 @@
       <c r="B16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="46">
+      <c r="C16" s="44">
         <v>312</v>
       </c>
-      <c r="D16" s="46"/>
+      <c r="D16" s="44"/>
       <c r="E16" s="42">
         <v>0</v>
       </c>
       <c r="F16" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="48" t="s">
+      <c r="G16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H16" s="53">
+      <c r="H16" s="51">
         <v>312</v>
       </c>
-      <c r="I16" s="54">
+      <c r="I16" s="52">
         <v>0</v>
       </c>
     </row>
@@ -4072,23 +4068,23 @@
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="46">
+      <c r="C17" s="44">
         <v>312</v>
       </c>
-      <c r="D17" s="46"/>
+      <c r="D17" s="44"/>
       <c r="E17" s="42">
         <v>0</v>
       </c>
       <c r="F17" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="48" t="s">
+      <c r="G17" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H17" s="53">
+      <c r="H17" s="51">
         <v>312</v>
       </c>
-      <c r="I17" s="54">
+      <c r="I17" s="52">
         <v>0</v>
       </c>
     </row>
@@ -4099,23 +4095,23 @@
       <c r="B18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="46">
+      <c r="C18" s="44">
         <v>312</v>
       </c>
-      <c r="D18" s="46"/>
+      <c r="D18" s="44"/>
       <c r="E18" s="42">
         <v>0</v>
       </c>
       <c r="F18" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="48" t="s">
+      <c r="G18" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H18" s="53">
+      <c r="H18" s="51">
         <v>312</v>
       </c>
-      <c r="I18" s="54">
+      <c r="I18" s="52">
         <v>0</v>
       </c>
     </row>
@@ -4126,23 +4122,23 @@
       <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="46">
+      <c r="C19" s="44">
         <v>312</v>
       </c>
-      <c r="D19" s="46"/>
+      <c r="D19" s="44"/>
       <c r="E19" s="42">
         <v>0</v>
       </c>
       <c r="F19" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="48" t="s">
+      <c r="G19" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H19" s="53">
+      <c r="H19" s="51">
         <v>312</v>
       </c>
-      <c r="I19" s="54">
+      <c r="I19" s="52">
         <v>0</v>
       </c>
     </row>
@@ -4159,13 +4155,13 @@
       <c r="F20" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="55" t="s">
+      <c r="G20" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="H20" s="55" t="s">
+      <c r="H20" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="I20" s="55" t="s">
+      <c r="I20" s="53" t="s">
         <v>12</v>
       </c>
     </row>
@@ -4176,23 +4172,23 @@
       <c r="B21" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="42">
+      <c r="C21" s="59">
         <v>344</v>
       </c>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56">
+      <c r="D21" s="42"/>
+      <c r="E21" s="54">
         <v>0</v>
       </c>
       <c r="F21" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="50" t="s">
+      <c r="G21" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="H21" s="51">
+      <c r="H21" s="49">
         <v>344</v>
       </c>
-      <c r="I21" s="52">
+      <c r="I21" s="50">
         <v>0</v>
       </c>
     </row>
@@ -4203,23 +4199,23 @@
       <c r="B22" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="57">
+      <c r="C22" s="55">
         <v>344</v>
       </c>
-      <c r="D22" s="60"/>
-      <c r="E22" s="44">
+      <c r="D22" s="42"/>
+      <c r="E22" s="60">
         <v>400</v>
       </c>
-      <c r="F22" s="48">
+      <c r="F22" s="46">
         <v>2024</v>
       </c>
-      <c r="G22" s="48" t="s">
+      <c r="G22" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H22" s="53">
-        <v>0</v>
-      </c>
-      <c r="I22" s="54">
+      <c r="H22" s="51">
+        <v>0</v>
+      </c>
+      <c r="I22" s="52">
         <v>56</v>
       </c>
     </row>
@@ -4230,23 +4226,23 @@
       <c r="B23" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="57">
+      <c r="C23" s="55">
         <v>344</v>
       </c>
-      <c r="D23" s="60"/>
-      <c r="E23" s="45">
+      <c r="D23" s="42"/>
+      <c r="E23" s="61">
         <v>400</v>
       </c>
-      <c r="F23" s="48">
+      <c r="F23" s="46">
         <v>2025</v>
       </c>
-      <c r="G23" s="48" t="s">
+      <c r="G23" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H23" s="53">
-        <v>0</v>
-      </c>
-      <c r="I23" s="54">
+      <c r="H23" s="51">
+        <v>0</v>
+      </c>
+      <c r="I23" s="52">
         <v>56</v>
       </c>
     </row>
@@ -4257,23 +4253,23 @@
       <c r="B24" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="57">
+      <c r="C24" s="55">
         <v>344</v>
       </c>
-      <c r="D24" s="60"/>
-      <c r="E24" s="45">
+      <c r="D24" s="42"/>
+      <c r="E24" s="61">
         <v>400</v>
       </c>
-      <c r="F24" s="48">
+      <c r="F24" s="46">
         <v>2025</v>
       </c>
-      <c r="G24" s="48" t="s">
+      <c r="G24" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H24" s="53">
-        <v>0</v>
-      </c>
-      <c r="I24" s="54">
+      <c r="H24" s="51">
+        <v>0</v>
+      </c>
+      <c r="I24" s="52">
         <v>56</v>
       </c>
     </row>
@@ -4284,23 +4280,23 @@
       <c r="B25" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="57">
+      <c r="C25" s="55">
         <v>344</v>
       </c>
-      <c r="D25" s="60"/>
-      <c r="E25" s="45">
+      <c r="D25" s="42"/>
+      <c r="E25" s="61">
         <v>400</v>
       </c>
-      <c r="F25" s="48">
+      <c r="F25" s="46">
         <v>2024</v>
       </c>
-      <c r="G25" s="48" t="s">
+      <c r="G25" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H25" s="53">
-        <v>0</v>
-      </c>
-      <c r="I25" s="54">
+      <c r="H25" s="51">
+        <v>0</v>
+      </c>
+      <c r="I25" s="52">
         <v>56</v>
       </c>
     </row>
@@ -4311,23 +4307,23 @@
       <c r="B26" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="57">
+      <c r="C26" s="55">
         <v>344</v>
       </c>
-      <c r="D26" s="60"/>
-      <c r="E26" s="45">
+      <c r="D26" s="42"/>
+      <c r="E26" s="61">
         <v>400</v>
       </c>
-      <c r="F26" s="48">
+      <c r="F26" s="46">
         <v>2024</v>
       </c>
-      <c r="G26" s="48" t="s">
+      <c r="G26" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H26" s="53">
-        <v>0</v>
-      </c>
-      <c r="I26" s="54">
+      <c r="H26" s="51">
+        <v>0</v>
+      </c>
+      <c r="I26" s="52">
         <v>56</v>
       </c>
     </row>
@@ -4338,23 +4334,23 @@
       <c r="B27" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="57">
+      <c r="C27" s="55">
         <v>344</v>
       </c>
-      <c r="D27" s="60"/>
-      <c r="E27" s="45">
+      <c r="D27" s="42"/>
+      <c r="E27" s="61">
         <v>400</v>
       </c>
-      <c r="F27" s="48">
+      <c r="F27" s="46">
         <v>2024</v>
       </c>
-      <c r="G27" s="48" t="s">
+      <c r="G27" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H27" s="53">
-        <v>0</v>
-      </c>
-      <c r="I27" s="54">
+      <c r="H27" s="51">
+        <v>0</v>
+      </c>
+      <c r="I27" s="52">
         <v>56</v>
       </c>
     </row>
@@ -4365,23 +4361,23 @@
       <c r="B28" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="46">
+      <c r="C28" s="55">
         <v>344</v>
       </c>
-      <c r="D28" s="48"/>
-      <c r="E28" s="48">
+      <c r="D28" s="42"/>
+      <c r="E28" s="46">
         <v>0</v>
       </c>
       <c r="F28" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G28" s="48" t="s">
+      <c r="G28" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H28" s="53">
+      <c r="H28" s="51">
         <v>344</v>
       </c>
-      <c r="I28" s="54">
+      <c r="I28" s="52">
         <v>0</v>
       </c>
     </row>
@@ -4392,23 +4388,23 @@
       <c r="B29" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C29" s="46">
+      <c r="C29" s="55">
         <v>344</v>
       </c>
-      <c r="D29" s="46"/>
-      <c r="E29" s="42">
+      <c r="D29" s="42"/>
+      <c r="E29" s="48">
         <v>0</v>
       </c>
       <c r="F29" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="48" t="s">
+      <c r="G29" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H29" s="53">
+      <c r="H29" s="51">
         <v>344</v>
       </c>
-      <c r="I29" s="54">
+      <c r="I29" s="52">
         <v>0</v>
       </c>
     </row>
@@ -4425,13 +4421,13 @@
       <c r="F30" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="55" t="s">
+      <c r="G30" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="H30" s="55" t="s">
+      <c r="H30" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="55" t="s">
+      <c r="I30" s="53" t="s">
         <v>12</v>
       </c>
     </row>
@@ -4452,13 +4448,13 @@
       <c r="F31" s="42">
         <v>2025</v>
       </c>
-      <c r="G31" s="50" t="s">
+      <c r="G31" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="H31" s="51">
-        <v>0</v>
-      </c>
-      <c r="I31" s="52">
+      <c r="H31" s="49">
+        <v>0</v>
+      </c>
+      <c r="I31" s="50">
         <v>93</v>
       </c>
     </row>
@@ -4469,23 +4465,23 @@
       <c r="B32" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="46">
+      <c r="C32" s="44">
         <v>307</v>
       </c>
-      <c r="D32" s="46"/>
+      <c r="D32" s="44"/>
       <c r="E32" s="42">
         <v>0</v>
       </c>
       <c r="F32" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="48" t="s">
+      <c r="G32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="53">
+      <c r="H32" s="51">
         <v>307</v>
       </c>
-      <c r="I32" s="54">
+      <c r="I32" s="52">
         <v>0</v>
       </c>
     </row>
@@ -4496,23 +4492,23 @@
       <c r="B33" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="46">
+      <c r="C33" s="44">
         <v>307</v>
       </c>
-      <c r="D33" s="46"/>
+      <c r="D33" s="44"/>
       <c r="E33" s="42">
         <v>0</v>
       </c>
       <c r="F33" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G33" s="48" t="s">
+      <c r="G33" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H33" s="53">
+      <c r="H33" s="51">
         <v>307</v>
       </c>
-      <c r="I33" s="54">
+      <c r="I33" s="52">
         <v>0</v>
       </c>
     </row>
@@ -4523,23 +4519,23 @@
       <c r="B34" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="46">
+      <c r="C34" s="44">
         <v>307</v>
       </c>
-      <c r="D34" s="46"/>
+      <c r="D34" s="44"/>
       <c r="E34" s="42">
         <v>0</v>
       </c>
       <c r="F34" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G34" s="48" t="s">
+      <c r="G34" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H34" s="53">
+      <c r="H34" s="51">
         <v>307</v>
       </c>
-      <c r="I34" s="54">
+      <c r="I34" s="52">
         <v>0</v>
       </c>
     </row>
@@ -4550,23 +4546,23 @@
       <c r="B35" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C35" s="46">
+      <c r="C35" s="44">
         <v>307</v>
       </c>
-      <c r="D35" s="46"/>
+      <c r="D35" s="44"/>
       <c r="E35" s="42">
         <v>400</v>
       </c>
       <c r="F35" s="42">
         <v>2025</v>
       </c>
-      <c r="G35" s="48" t="s">
+      <c r="G35" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H35" s="53">
-        <v>0</v>
-      </c>
-      <c r="I35" s="54">
+      <c r="H35" s="51">
+        <v>0</v>
+      </c>
+      <c r="I35" s="52">
         <v>93</v>
       </c>
     </row>
@@ -4577,23 +4573,23 @@
       <c r="B36" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C36" s="46">
+      <c r="C36" s="44">
         <v>307</v>
       </c>
-      <c r="D36" s="46"/>
+      <c r="D36" s="44"/>
       <c r="E36" s="42">
         <v>350</v>
       </c>
       <c r="F36" s="42">
         <v>2025</v>
       </c>
-      <c r="G36" s="48" t="s">
+      <c r="G36" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H36" s="53">
-        <v>0</v>
-      </c>
-      <c r="I36" s="54">
+      <c r="H36" s="51">
+        <v>0</v>
+      </c>
+      <c r="I36" s="52">
         <v>43</v>
       </c>
     </row>
@@ -4604,23 +4600,23 @@
       <c r="B37" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C37" s="46">
+      <c r="C37" s="44">
         <v>307</v>
       </c>
-      <c r="D37" s="46"/>
+      <c r="D37" s="44"/>
       <c r="E37" s="42">
         <v>400</v>
       </c>
       <c r="F37" s="42">
         <v>2025</v>
       </c>
-      <c r="G37" s="48" t="s">
+      <c r="G37" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H37" s="53">
-        <v>0</v>
-      </c>
-      <c r="I37" s="54">
+      <c r="H37" s="51">
+        <v>0</v>
+      </c>
+      <c r="I37" s="52">
         <v>93</v>
       </c>
     </row>
@@ -4631,23 +4627,23 @@
       <c r="B38" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="46">
+      <c r="C38" s="44">
         <v>307</v>
       </c>
-      <c r="D38" s="46"/>
+      <c r="D38" s="44"/>
       <c r="E38" s="42">
         <v>0</v>
       </c>
       <c r="F38" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G38" s="48" t="s">
+      <c r="G38" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H38" s="53">
+      <c r="H38" s="51">
         <v>307</v>
       </c>
-      <c r="I38" s="54">
+      <c r="I38" s="52">
         <v>0</v>
       </c>
     </row>
@@ -4658,23 +4654,23 @@
       <c r="B39" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C39" s="46">
+      <c r="C39" s="44">
         <v>307</v>
       </c>
-      <c r="D39" s="46"/>
+      <c r="D39" s="44"/>
       <c r="E39" s="42">
         <v>0</v>
       </c>
       <c r="F39" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G39" s="48" t="s">
+      <c r="G39" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H39" s="53">
+      <c r="H39" s="51">
         <v>307</v>
       </c>
-      <c r="I39" s="54">
+      <c r="I39" s="52">
         <v>0</v>
       </c>
     </row>
@@ -4691,13 +4687,13 @@
       <c r="F40" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="G40" s="55" t="s">
+      <c r="G40" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="H40" s="55" t="s">
+      <c r="H40" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="I40" s="55" t="s">
+      <c r="I40" s="53" t="s">
         <v>12</v>
       </c>
     </row>
@@ -4718,13 +4714,13 @@
       <c r="F41" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G41" s="50" t="s">
+      <c r="G41" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="H41" s="51">
+      <c r="H41" s="49">
         <v>299</v>
       </c>
-      <c r="I41" s="52">
+      <c r="I41" s="50">
         <v>0</v>
       </c>
     </row>
@@ -4735,23 +4731,23 @@
       <c r="B42" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C42" s="46">
+      <c r="C42" s="44">
         <v>299</v>
       </c>
-      <c r="D42" s="46"/>
+      <c r="D42" s="44"/>
       <c r="E42" s="42">
         <v>0</v>
       </c>
       <c r="F42" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G42" s="48" t="s">
+      <c r="G42" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H42" s="53">
+      <c r="H42" s="51">
         <v>299</v>
       </c>
-      <c r="I42" s="54">
+      <c r="I42" s="52">
         <v>0</v>
       </c>
     </row>
@@ -4762,23 +4758,23 @@
       <c r="B43" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C43" s="46">
+      <c r="C43" s="44">
         <v>299</v>
       </c>
-      <c r="D43" s="46"/>
+      <c r="D43" s="44"/>
       <c r="E43" s="42">
         <v>0</v>
       </c>
       <c r="F43" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G43" s="48" t="s">
+      <c r="G43" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H43" s="53">
+      <c r="H43" s="51">
         <v>299</v>
       </c>
-      <c r="I43" s="54">
+      <c r="I43" s="52">
         <v>0</v>
       </c>
     </row>
@@ -4789,23 +4785,23 @@
       <c r="B44" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C44" s="46">
+      <c r="C44" s="44">
         <v>299</v>
       </c>
-      <c r="D44" s="46"/>
+      <c r="D44" s="44"/>
       <c r="E44" s="42">
         <v>0</v>
       </c>
       <c r="F44" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G44" s="48" t="s">
+      <c r="G44" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H44" s="53">
+      <c r="H44" s="51">
         <v>299</v>
       </c>
-      <c r="I44" s="54">
+      <c r="I44" s="52">
         <v>0</v>
       </c>
     </row>
@@ -4816,23 +4812,23 @@
       <c r="B45" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C45" s="46">
+      <c r="C45" s="44">
         <v>299</v>
       </c>
-      <c r="D45" s="46"/>
+      <c r="D45" s="44"/>
       <c r="E45" s="42">
         <v>0</v>
       </c>
       <c r="F45" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G45" s="48" t="s">
+      <c r="G45" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H45" s="53">
+      <c r="H45" s="51">
         <v>299</v>
       </c>
-      <c r="I45" s="54">
+      <c r="I45" s="52">
         <v>0</v>
       </c>
     </row>
@@ -4843,23 +4839,23 @@
       <c r="B46" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C46" s="46">
+      <c r="C46" s="44">
         <v>299</v>
       </c>
-      <c r="D46" s="46"/>
+      <c r="D46" s="44"/>
       <c r="E46" s="42">
         <v>0</v>
       </c>
       <c r="F46" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G46" s="48" t="s">
+      <c r="G46" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H46" s="53">
+      <c r="H46" s="51">
         <v>299</v>
       </c>
-      <c r="I46" s="54">
+      <c r="I46" s="52">
         <v>0</v>
       </c>
     </row>
@@ -4870,23 +4866,23 @@
       <c r="B47" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C47" s="46">
+      <c r="C47" s="44">
         <v>299</v>
       </c>
-      <c r="D47" s="46"/>
+      <c r="D47" s="44"/>
       <c r="E47" s="42">
         <v>0</v>
       </c>
       <c r="F47" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G47" s="48" t="s">
+      <c r="G47" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H47" s="53">
+      <c r="H47" s="51">
         <v>299</v>
       </c>
-      <c r="I47" s="54">
+      <c r="I47" s="52">
         <v>0</v>
       </c>
     </row>
@@ -4897,23 +4893,23 @@
       <c r="B48" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C48" s="46">
+      <c r="C48" s="44">
         <v>299</v>
       </c>
-      <c r="D48" s="46"/>
+      <c r="D48" s="44"/>
       <c r="E48" s="42">
         <v>0</v>
       </c>
       <c r="F48" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G48" s="48" t="s">
+      <c r="G48" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H48" s="53">
+      <c r="H48" s="51">
         <v>299</v>
       </c>
-      <c r="I48" s="54">
+      <c r="I48" s="52">
         <v>0</v>
       </c>
     </row>
@@ -4924,23 +4920,23 @@
       <c r="B49" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C49" s="46">
+      <c r="C49" s="44">
         <v>299</v>
       </c>
-      <c r="D49" s="46"/>
+      <c r="D49" s="44"/>
       <c r="E49" s="42">
         <v>0</v>
       </c>
       <c r="F49" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="G49" s="48" t="s">
+      <c r="G49" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H49" s="53">
+      <c r="H49" s="51">
         <v>299</v>
       </c>
-      <c r="I49" s="54">
+      <c r="I49" s="52">
         <v>0</v>
       </c>
     </row>
@@ -5930,11 +5926,11 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F81:F89 F91:F98 F71:F79 F51:F59 F61:F69" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G61:G69 G71:G79 G81:G89 G91:G98 G51:G59" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F91:F98 F81:F89 F71:F79 F61:F69 F51:F59 F41:F49 F31:F39 F21:F29 F14:F19 F8:F12 F2:F6" xr:uid="{898554D8-A0FD-40AE-A340-41919F270F28}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5946,7 +5942,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -6046,10 +6042,10 @@
       <c r="L2" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="M2" s="58" t="s">
+      <c r="M2" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="N2" s="58" t="s">
+      <c r="N2" s="56" t="s">
         <v>49</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -6082,10 +6078,10 @@
       <c r="X2" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="Y2" s="59" t="s">
+      <c r="Y2" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="Z2" s="59" t="s">
+      <c r="Z2" s="57" t="s">
         <v>61</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -7603,12 +7599,18 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2496</v>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="5"/>
+      <c r="E26" s="5">
+        <v>261</v>
+      </c>
+      <c r="F26" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="H26" s="5">
         <f t="shared" si="2"/>
-        <v>2496</v>
+        <v>2235</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="3"/>
@@ -7674,12 +7676,18 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2496</v>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="5"/>
+      <c r="E27" s="5">
+        <v>261</v>
+      </c>
+      <c r="F27" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="H27" s="5">
         <f t="shared" si="2"/>
-        <v>2496</v>
+        <v>2235</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="3"/>
@@ -7745,12 +7753,18 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2496</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="5"/>
+      <c r="E28" s="5">
+        <v>261</v>
+      </c>
+      <c r="F28" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="H28" s="5">
         <f t="shared" si="2"/>
-        <v>2496</v>
+        <v>2235</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="3"/>
@@ -7816,12 +7830,18 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2496</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="5"/>
+      <c r="E29" s="5">
+        <v>261</v>
+      </c>
+      <c r="F29" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="H29" s="5">
         <f>IF((D29-E29)&lt;0,0,(D29-E29))</f>
-        <v>2496</v>
+        <v>2235</v>
       </c>
       <c r="I29" s="5">
         <f>IF((E29-D29)&lt;0,0,(E29-D29))</f>
@@ -9177,13 +9197,17 @@
         <v>2456</v>
       </c>
       <c r="E49" s="5">
-        <v>0</v>
-      </c>
-      <c r="F49" s="1"/>
-      <c r="G49" s="5"/>
+        <v>160</v>
+      </c>
+      <c r="F49" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="H49" s="5">
         <f t="shared" si="2"/>
-        <v>2456</v>
+        <v>2296</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="3"/>
@@ -9326,12 +9350,18 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2456</v>
       </c>
-      <c r="E51" s="5"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="5"/>
+      <c r="E51" s="5">
+        <v>160</v>
+      </c>
+      <c r="F51" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="H51" s="5">
         <f t="shared" si="2"/>
-        <v>2456</v>
+        <v>2296</v>
       </c>
       <c r="I51" s="5">
         <f t="shared" si="3"/>
@@ -14142,191 +14172,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
-    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D23:F31 D43:F51" name="LAS"/>
+    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G33:G41 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110 G23:G31 G43:G51" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -14339,10 +14189,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G103:G110 G33:G41 G23:G31 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G43:G51" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14358,7 +14208,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -14458,10 +14308,10 @@
       <c r="L2" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="M2" s="58" t="s">
+      <c r="M2" s="56" t="s">
         <v>75</v>
       </c>
-      <c r="N2" s="58" t="s">
+      <c r="N2" s="56" t="s">
         <v>76</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -14494,10 +14344,10 @@
       <c r="X2" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="Y2" s="59" t="s">
+      <c r="Y2" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="Z2" s="59" t="s">
+      <c r="Z2" s="57" t="s">
         <v>88</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -15660,9 +15510,9 @@
       </c>
     </row>
     <row r="20" spans="1:27" s="7" customFormat="1" ht="15">
-      <c r="W20" s="61"/>
-      <c r="X20" s="61"/>
-      <c r="Y20" s="61"/>
+      <c r="W20" s="58"/>
+      <c r="X20" s="58"/>
+      <c r="Y20" s="58"/>
     </row>
     <row r="21" spans="1:27" ht="38.25">
       <c r="A21" s="1">
@@ -17894,13 +17744,13 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2392</v>
       </c>
-      <c r="E55" s="49">
+      <c r="E55" s="47">
         <v>150</v>
       </c>
       <c r="F55" s="1">
         <v>2025</v>
       </c>
-      <c r="G55" s="49" t="s">
+      <c r="G55" s="47" t="s">
         <v>64</v>
       </c>
       <c r="H55" s="5">
@@ -17915,13 +17765,13 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2392</v>
       </c>
-      <c r="K55" s="49">
+      <c r="K55" s="47">
         <v>150</v>
       </c>
       <c r="L55" s="40">
         <v>2025</v>
       </c>
-      <c r="M55" s="49" t="s">
+      <c r="M55" s="47" t="s">
         <v>64</v>
       </c>
       <c r="N55" s="5">
@@ -17936,13 +17786,13 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2392</v>
       </c>
-      <c r="Q55" s="49">
+      <c r="Q55" s="47">
         <v>350</v>
       </c>
       <c r="R55" s="40">
         <v>2025</v>
       </c>
-      <c r="S55" s="49" t="s">
+      <c r="S55" s="47" t="s">
         <v>64</v>
       </c>
       <c r="T55" s="5">
@@ -17983,13 +17833,13 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2392</v>
       </c>
-      <c r="E56" s="47">
+      <c r="E56" s="45">
         <v>350</v>
       </c>
       <c r="F56" s="1">
         <v>2025</v>
       </c>
-      <c r="G56" s="47" t="s">
+      <c r="G56" s="45" t="s">
         <v>64</v>
       </c>
       <c r="H56" s="5">
@@ -18004,13 +17854,13 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2392</v>
       </c>
-      <c r="K56" s="47">
+      <c r="K56" s="45">
         <v>350</v>
       </c>
       <c r="L56" s="40">
         <v>2025</v>
       </c>
-      <c r="M56" s="47" t="s">
+      <c r="M56" s="45" t="s">
         <v>64</v>
       </c>
       <c r="N56" s="5">
@@ -18025,13 +17875,13 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2392</v>
       </c>
-      <c r="Q56" s="47">
+      <c r="Q56" s="45">
         <v>350</v>
       </c>
       <c r="R56" s="40">
         <v>2025</v>
       </c>
-      <c r="S56" s="47" t="s">
+      <c r="S56" s="45" t="s">
         <v>64</v>
       </c>
       <c r="T56" s="5">
@@ -18072,13 +17922,13 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2392</v>
       </c>
-      <c r="E57" s="47">
+      <c r="E57" s="45">
         <v>350</v>
       </c>
       <c r="F57" s="1">
         <v>2025</v>
       </c>
-      <c r="G57" s="47" t="s">
+      <c r="G57" s="45" t="s">
         <v>64</v>
       </c>
       <c r="H57" s="5">
@@ -18093,13 +17943,13 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2392</v>
       </c>
-      <c r="K57" s="47">
+      <c r="K57" s="45">
         <v>350</v>
       </c>
       <c r="L57" s="40">
         <v>2025</v>
       </c>
-      <c r="M57" s="47" t="s">
+      <c r="M57" s="45" t="s">
         <v>64</v>
       </c>
       <c r="N57" s="5">
@@ -18114,13 +17964,13 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2392</v>
       </c>
-      <c r="Q57" s="47">
+      <c r="Q57" s="45">
         <v>350</v>
       </c>
       <c r="R57" s="40">
         <v>2025</v>
       </c>
-      <c r="S57" s="47" t="s">
+      <c r="S57" s="45" t="s">
         <v>64</v>
       </c>
       <c r="T57" s="5">
@@ -18191,13 +18041,13 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2392</v>
       </c>
-      <c r="Q58" s="47">
+      <c r="Q58" s="45">
         <v>350</v>
       </c>
       <c r="R58" s="40">
         <v>2025</v>
       </c>
-      <c r="S58" s="47" t="s">
+      <c r="S58" s="45" t="s">
         <v>64</v>
       </c>
       <c r="T58" s="5">
@@ -18268,13 +18118,13 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2392</v>
       </c>
-      <c r="Q59" s="47">
+      <c r="Q59" s="45">
         <v>350</v>
       </c>
       <c r="R59" s="40">
         <v>2025</v>
       </c>
-      <c r="S59" s="47" t="s">
+      <c r="S59" s="45" t="s">
         <v>64</v>
       </c>
       <c r="T59" s="5">
@@ -18345,13 +18195,13 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2392</v>
       </c>
-      <c r="Q60" s="47">
+      <c r="Q60" s="45">
         <v>350</v>
       </c>
       <c r="R60" s="40">
         <v>2025</v>
       </c>
-      <c r="S60" s="47" t="s">
+      <c r="S60" s="45" t="s">
         <v>64</v>
       </c>
       <c r="T60" s="5">
@@ -18422,13 +18272,13 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2392</v>
       </c>
-      <c r="Q61" s="47">
+      <c r="Q61" s="45">
         <v>350</v>
       </c>
       <c r="R61" s="40">
         <v>2025</v>
       </c>
-      <c r="S61" s="47" t="s">
+      <c r="S61" s="45" t="s">
         <v>64</v>
       </c>
       <c r="T61" s="5">
@@ -18499,13 +18349,13 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2392</v>
       </c>
-      <c r="Q62" s="47">
+      <c r="Q62" s="45">
         <v>350</v>
       </c>
       <c r="R62" s="40">
         <v>2025</v>
       </c>
-      <c r="S62" s="47" t="s">
+      <c r="S62" s="45" t="s">
         <v>64</v>
       </c>
       <c r="T62" s="5">
@@ -18576,13 +18426,13 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2392</v>
       </c>
-      <c r="Q63" s="47">
+      <c r="Q63" s="45">
         <v>0</v>
       </c>
       <c r="R63" s="40">
         <v>0</v>
       </c>
-      <c r="S63" s="47" t="s">
+      <c r="S63" s="45" t="s">
         <v>12</v>
       </c>
       <c r="T63" s="5">
@@ -18653,13 +18503,13 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2392</v>
       </c>
-      <c r="Q64" s="47">
+      <c r="Q64" s="45">
         <v>350</v>
       </c>
       <c r="R64" s="40">
         <v>2025</v>
       </c>
-      <c r="S64" s="47" t="s">
+      <c r="S64" s="45" t="s">
         <v>64</v>
       </c>
       <c r="T64" s="5">
@@ -18730,13 +18580,13 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2392</v>
       </c>
-      <c r="Q65" s="47">
+      <c r="Q65" s="45">
         <v>350</v>
       </c>
       <c r="R65" s="40">
         <v>2025</v>
       </c>
-      <c r="S65" s="47" t="s">
+      <c r="S65" s="45" t="s">
         <v>64</v>
       </c>
       <c r="T65" s="5">
@@ -22867,186 +22717,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101 C31:C41 C43:C53 C55:C65" name="Textbooks"/>
@@ -23068,8 +22738,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 M103:M113 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 M115:M122 Y55:Y65 M58:M65 G58:G65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 Y21:Y29" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X12:X19 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 L115:L122 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 F55:F65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 L58:L65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F103:F113 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 X21:X29" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{D5A3151C-D0D3-4258-8EF8-DCBF92811633}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
